--- a/main/ig/ValueSet-fr-core-vs-mode-validation-identity-ins.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-mode-validation-identity-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:34:41+00:00</t>
+    <t>2026-09-17T13:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-mode-validation-identity-ins.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-mode-validation-identity-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:31:08+00:00</t>
+    <t>2026-10-12T16:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,16 +105,40 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>CN</t>
+  </si>
+  <si>
     <t>PA</t>
   </si>
   <si>
-    <t>CN</t>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>eCN</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>AV</t>
+  </si>
+  <si>
+    <t>LECV</t>
   </si>
   <si>
     <t>AN</t>
   </si>
   <si>
     <t>LE</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>CIMS</t>
+  </si>
+  <si>
+    <t>ANCV</t>
   </si>
   <si>
     <t/>
@@ -395,7 +419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -438,16 +462,64 @@
       <c r="A6" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B6" t="s" s="2">
-        <v>34</v>
-      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>36</v>
+      </c>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
